--- a/artfynd/A 41729-2025 artfynd.xlsx
+++ b/artfynd/A 41729-2025 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128817873</v>
+        <v>128817872</v>
       </c>
       <c r="B3" t="n">
-        <v>58151</v>
+        <v>58146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,26 +805,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102999</v>
+        <v>103001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128817872</v>
+        <v>128817873</v>
       </c>
       <c r="B4" t="n">
-        <v>58146</v>
+        <v>58151</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,26 +924,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103001</v>
+        <v>102999</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -995,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">

--- a/artfynd/A 41729-2025 artfynd.xlsx
+++ b/artfynd/A 41729-2025 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128817872</v>
+        <v>128817873</v>
       </c>
       <c r="B3" t="n">
-        <v>58146</v>
+        <v>58151</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,26 +805,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103001</v>
+        <v>102999</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128817873</v>
+        <v>128817872</v>
       </c>
       <c r="B4" t="n">
-        <v>58151</v>
+        <v>58146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,26 +924,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102999</v>
+        <v>103001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -995,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">

--- a/artfynd/A 41729-2025 artfynd.xlsx
+++ b/artfynd/A 41729-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128817869</v>
       </c>
       <c r="B2" t="n">
-        <v>57846</v>
+        <v>57850</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128817872</v>
       </c>
       <c r="B3" t="n">
-        <v>58146</v>
+        <v>58150</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>128817873</v>
       </c>
       <c r="B4" t="n">
-        <v>58151</v>
+        <v>58155</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41729-2025 artfynd.xlsx
+++ b/artfynd/A 41729-2025 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128817872</v>
+        <v>128817873</v>
       </c>
       <c r="B3" t="n">
-        <v>58150</v>
+        <v>58155</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,26 +805,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103001</v>
+        <v>102999</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128817873</v>
+        <v>128817872</v>
       </c>
       <c r="B4" t="n">
-        <v>58155</v>
+        <v>58150</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,26 +924,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102999</v>
+        <v>103001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -995,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">

--- a/artfynd/A 41729-2025 artfynd.xlsx
+++ b/artfynd/A 41729-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128817869</v>
       </c>
       <c r="B2" t="n">
-        <v>57850</v>
+        <v>57853</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128817873</v>
       </c>
       <c r="B3" t="n">
-        <v>58155</v>
+        <v>58158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>128817872</v>
       </c>
       <c r="B4" t="n">
-        <v>58150</v>
+        <v>58153</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41729-2025 artfynd.xlsx
+++ b/artfynd/A 41729-2025 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128817873</v>
+        <v>128817872</v>
       </c>
       <c r="B3" t="n">
-        <v>58158</v>
+        <v>58153</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,26 +805,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102999</v>
+        <v>103001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128817872</v>
+        <v>128817873</v>
       </c>
       <c r="B4" t="n">
-        <v>58153</v>
+        <v>58158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,26 +924,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103001</v>
+        <v>102999</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -995,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">

--- a/artfynd/A 41729-2025 artfynd.xlsx
+++ b/artfynd/A 41729-2025 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128817872</v>
+        <v>128817873</v>
       </c>
       <c r="B3" t="n">
-        <v>58153</v>
+        <v>58158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,26 +805,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103001</v>
+        <v>102999</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128817873</v>
+        <v>128817872</v>
       </c>
       <c r="B4" t="n">
-        <v>58158</v>
+        <v>58153</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,26 +924,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102999</v>
+        <v>103001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -995,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">

--- a/artfynd/A 41729-2025 artfynd.xlsx
+++ b/artfynd/A 41729-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128817869</v>
       </c>
       <c r="B2" t="n">
-        <v>57853</v>
+        <v>57855</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128817873</v>
       </c>
       <c r="B3" t="n">
-        <v>58158</v>
+        <v>58160</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>128817872</v>
       </c>
       <c r="B4" t="n">
-        <v>58153</v>
+        <v>58155</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41729-2025 artfynd.xlsx
+++ b/artfynd/A 41729-2025 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128817873</v>
+        <v>128817872</v>
       </c>
       <c r="B3" t="n">
-        <v>58160</v>
+        <v>58155</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,26 +805,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102999</v>
+        <v>103001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128817872</v>
+        <v>128817873</v>
       </c>
       <c r="B4" t="n">
-        <v>58155</v>
+        <v>58160</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,26 +924,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103001</v>
+        <v>102999</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -995,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">

--- a/artfynd/A 41729-2025 artfynd.xlsx
+++ b/artfynd/A 41729-2025 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128817872</v>
+        <v>128817873</v>
       </c>
       <c r="B3" t="n">
-        <v>58155</v>
+        <v>58160</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,26 +805,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103001</v>
+        <v>102999</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128817873</v>
+        <v>128817872</v>
       </c>
       <c r="B4" t="n">
-        <v>58160</v>
+        <v>58155</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,26 +924,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102999</v>
+        <v>103001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -995,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">

--- a/artfynd/A 41729-2025 artfynd.xlsx
+++ b/artfynd/A 41729-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128817869</v>
       </c>
       <c r="B2" t="n">
-        <v>57855</v>
+        <v>57857</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128817873</v>
       </c>
       <c r="B3" t="n">
-        <v>58160</v>
+        <v>58162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>128817872</v>
       </c>
       <c r="B4" t="n">
-        <v>58155</v>
+        <v>58157</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41729-2025 artfynd.xlsx
+++ b/artfynd/A 41729-2025 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128817873</v>
+        <v>128817872</v>
       </c>
       <c r="B3" t="n">
-        <v>58162</v>
+        <v>58157</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,26 +805,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102999</v>
+        <v>103001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128817872</v>
+        <v>128817873</v>
       </c>
       <c r="B4" t="n">
-        <v>58157</v>
+        <v>58162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,26 +924,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103001</v>
+        <v>102999</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -995,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">

--- a/artfynd/A 41729-2025 artfynd.xlsx
+++ b/artfynd/A 41729-2025 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128817872</v>
+        <v>128817873</v>
       </c>
       <c r="B3" t="n">
-        <v>58157</v>
+        <v>58162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,26 +805,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103001</v>
+        <v>102999</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128817873</v>
+        <v>128817872</v>
       </c>
       <c r="B4" t="n">
-        <v>58162</v>
+        <v>58157</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,26 +924,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102999</v>
+        <v>103001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -995,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">

--- a/artfynd/A 41729-2025 artfynd.xlsx
+++ b/artfynd/A 41729-2025 artfynd.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
